--- a/Gantt_IEE3896.xlsx
+++ b/Gantt_IEE3896.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/jmondacaf_uc_cl/Documents/Universidad/Décimo Semestre/Teoría y Diseño de Antenas/Proyecto/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{82B4E092-5790-49E9-B461-0DD5A29D4A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4FC638D-2830-4967-B188-EAA32A491A85}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,19 +22,22 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
   <si>
     <t>Carta Gantt · Radiotelescopio de HI (IEE3896, 2026-2)</t>
   </si>
   <si>
+    <t>◆ = Hito o entrega</t>
+  </si>
+  <si>
+    <t>Día 1</t>
+  </si>
+  <si>
     <t>Lunes de cada semana →</t>
   </si>
   <si>
@@ -89,27 +86,75 @@
     <t>◆ Registrar título y entregar Definición del Proyecto</t>
   </si>
   <si>
+    <t>Consultar viabilidad, reservar material y posibilidad de usar RFSoC</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
     <t>Pedir LNA + filtro de 1420 MHz</t>
   </si>
   <si>
+    <t>Retirar equipos e instalar/aprender bien a usar softwares correspondientes</t>
+  </si>
+  <si>
     <t>Programa de adquisición de datos (FFT, promedio, registro)</t>
   </si>
   <si>
+    <t>Cálculo analítico de la bocina y simulación en Ansys</t>
+  </si>
+  <si>
+    <t>Definir material y comprar/conseguir</t>
+  </si>
+  <si>
     <t>Construcción de la bocina</t>
   </si>
   <si>
     <t>Censo de interferencias (RFI) 1.3–1.5 GHz</t>
   </si>
   <si>
+    <t>Aprender RFSoC en el AIUC</t>
+  </si>
+  <si>
+    <t>Medición de S11 con la VNA y caracterización de la antena (patrón de radiación).</t>
+  </si>
+  <si>
     <t>Reporte de avance (redacción)</t>
   </si>
   <si>
+    <t>Configurar RFSoC</t>
+  </si>
+  <si>
     <t>◆ Entrega Reporte de avance</t>
   </si>
   <si>
+    <t>Comparar caracterización y simulación</t>
+  </si>
+  <si>
+    <t>Instalar horn en el sitio y calibrar</t>
+  </si>
+  <si>
+    <t>Primera detección de la línea de HI</t>
+  </si>
+  <si>
     <t>Reporte final: borrador, resultados y discusión</t>
   </si>
   <si>
+    <t>Observaciones y análisis de datos</t>
+  </si>
+  <si>
+    <t>Póster, demostración, y ensayo</t>
+  </si>
+  <si>
+    <t>Espectro con RFSoC</t>
+  </si>
+  <si>
+    <t>◆ Feria Científica</t>
+  </si>
+  <si>
+    <t>Reporte final</t>
+  </si>
+  <si>
     <t>◆ Entrega Reporte final</t>
   </si>
   <si>
@@ -123,187 +168,167 @@
   </si>
   <si>
     <t>Semana actual (encabezado)</t>
-  </si>
-  <si>
-    <t>◆ = Hito o entrega</t>
-  </si>
-  <si>
-    <t>Día 1</t>
-  </si>
-  <si>
-    <t>Consultar viabilidad, reservar material y posibilidad de usar RFSoC</t>
-  </si>
-  <si>
-    <t>Retirar equipos e instalar/aprender bien a usar softwares correspondientes</t>
-  </si>
-  <si>
-    <t>Cálculo analítico de la bocina y simulación en Ansys</t>
-  </si>
-  <si>
-    <t>Definir material y comprar/conseguir</t>
-  </si>
-  <si>
-    <t>Medición de S11 con la VNA y caracterización de la antena (patrón de radiación).</t>
-  </si>
-  <si>
-    <t>Aprender RFSoC en el AIUC</t>
-  </si>
-  <si>
-    <t>Configurar RFSoC</t>
-  </si>
-  <si>
-    <t>Comparar caracterización y simulación</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Instalar </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>horn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> en el sitio y calibrar</t>
-    </r>
-  </si>
-  <si>
-    <t>Primera detección de la línea de HI</t>
-  </si>
-  <si>
-    <t>Observaciones y análisis de datos</t>
-  </si>
-  <si>
-    <t>Póster, demostración, y ensayo</t>
-  </si>
-  <si>
-    <t>Espectro con RFSoC</t>
-  </si>
-  <si>
-    <t>◆ Feria Científica</t>
-  </si>
-  <si>
-    <t>Reporte final</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF475569"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF00B050"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -341,6 +366,12 @@
         <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -369,7 +400,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -406,11 +437,59 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -419,117 +498,45 @@
   <dxfs count="4">
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FF2563EB"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+          <bgColor rgb="FFFEF3C7"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDC2626"/>
+          <bgColor rgb="FFDC2626"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF59E0B"/>
           <bgColor rgb="FFF59E0B"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFDC2626"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEF3C7"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF2563EB"/>
+          <bgColor rgb="FF2563EB"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFDC2626"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF9C4"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCBD5E1"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFEF3C7"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF2563EB"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFF59E0B"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF475569"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF334155"/>
-      <rgbColor rgb="FF1E293B"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office Theme">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
@@ -567,7 +574,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office Theme">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -579,62 +586,35 @@
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Craft">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
@@ -653,48 +633,12 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-          <a:tileRect/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-          <a:tileRect/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -704,89 +648,89 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="92.42578125" customWidth="1"/>
-    <col min="3" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="14" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="5.00390625" customWidth="1"/>
+    <col min="2" max="2" width="92.421875" customWidth="1"/>
+    <col min="3" max="4" width="9.00390625" customWidth="1"/>
+    <col min="5" max="5" width="6.00390625" customWidth="1"/>
+    <col min="6" max="14" width="7.421875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" ht="19.09">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4">
         <v>46293</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="7" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6" s="9">
         <f>$E$3+0</f>
@@ -825,12 +769,12 @@
         <v>46349</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="10">
         <v>1</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="12">
         <v>46294</v>
@@ -839,7 +783,7 @@
         <v>46294</v>
       </c>
       <c r="E7" s="10">
-        <f t="shared" ref="E7:E30" si="0">D7-C7+1</f>
+        <f>D7-C7+1</f>
         <v>1</v>
       </c>
       <c r="F7" s="10"/>
@@ -852,12 +796,12 @@
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="19.5" customHeight="1">
       <c r="A8" s="10">
         <v>2</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C8" s="12">
         <v>46294</v>
@@ -866,11 +810,15 @@
         <v>46301</v>
       </c>
       <c r="E8" s="10">
-        <f t="shared" si="0"/>
+        <f>D8-C8+1</f>
         <v>8</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
+      <c r="F8" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
@@ -879,12 +827,12 @@
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
     </row>
-    <row r="9" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="10">
         <v>3</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C9" s="12">
         <v>46295</v>
@@ -893,7 +841,7 @@
         <v>46303</v>
       </c>
       <c r="E9" s="10">
-        <f t="shared" si="0"/>
+        <f>D9-C9+1</f>
         <v>9</v>
       </c>
       <c r="F9" s="10"/>
@@ -906,12 +854,12 @@
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="10">
         <v>4</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C10" s="12">
         <v>46300</v>
@@ -920,11 +868,13 @@
         <v>46303</v>
       </c>
       <c r="E10" s="10">
-        <f t="shared" si="0"/>
+        <f>D10-C10+1</f>
         <v>4</v>
       </c>
       <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="G10" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
@@ -933,12 +883,12 @@
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="10">
         <v>5</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>18</v>
+      <c r="B11" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="C11" s="12">
         <v>46302</v>
@@ -947,11 +897,13 @@
         <v>46305</v>
       </c>
       <c r="E11" s="10">
-        <f t="shared" si="0"/>
+        <f>D11-C11+1</f>
         <v>4</v>
       </c>
       <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="G11" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
@@ -960,12 +912,12 @@
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="10">
         <v>6</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C12" s="12">
         <v>46303</v>
@@ -974,12 +926,16 @@
         <v>46311</v>
       </c>
       <c r="E12" s="10">
-        <f t="shared" si="0"/>
+        <f>D12-C12+1</f>
         <v>9</v>
       </c>
       <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+      <c r="G12" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -987,12 +943,12 @@
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="19.5" customHeight="1">
       <c r="A13" s="10">
         <v>8</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C13" s="12">
         <v>46307</v>
@@ -1001,12 +957,14 @@
         <v>46309</v>
       </c>
       <c r="E13" s="10">
-        <f t="shared" si="0"/>
+        <f>D13-C13+1</f>
         <v>3</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+      <c r="H13" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -1014,12 +972,12 @@
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="10">
         <v>9</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C14" s="12">
         <v>46310</v>
@@ -1028,7 +986,7 @@
         <v>46320</v>
       </c>
       <c r="E14" s="10">
-        <f t="shared" si="0"/>
+        <f>D14-C14+1</f>
         <v>11</v>
       </c>
       <c r="F14" s="10"/>
@@ -1041,12 +999,12 @@
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="10">
         <v>10</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C15" s="12">
         <v>46314</v>
@@ -1055,7 +1013,7 @@
         <v>46318</v>
       </c>
       <c r="E15" s="10">
-        <f t="shared" si="0"/>
+        <f>D15-C15+1</f>
         <v>5</v>
       </c>
       <c r="F15" s="10"/>
@@ -1068,12 +1026,12 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="10">
         <v>11</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C16" s="12">
         <v>46314</v>
@@ -1082,7 +1040,7 @@
         <v>46318</v>
       </c>
       <c r="E16" s="10">
-        <f t="shared" si="0"/>
+        <f>D16-C16+1</f>
         <v>5</v>
       </c>
       <c r="F16" s="10"/>
@@ -1095,12 +1053,12 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="19.5" customHeight="1">
       <c r="A17" s="10">
         <v>12</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C17" s="12">
         <v>46321</v>
@@ -1109,7 +1067,7 @@
         <v>46328</v>
       </c>
       <c r="E17" s="10">
-        <f t="shared" si="0"/>
+        <f>D17-C17+1</f>
         <v>8</v>
       </c>
       <c r="F17" s="10"/>
@@ -1122,12 +1080,12 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="10">
         <v>13</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C18" s="12">
         <v>46323</v>
@@ -1136,7 +1094,7 @@
         <v>46329</v>
       </c>
       <c r="E18" s="10">
-        <f t="shared" si="0"/>
+        <f>D18-C18+1</f>
         <v>7</v>
       </c>
       <c r="F18" s="10"/>
@@ -1149,12 +1107,12 @@
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="19.5" customHeight="1">
       <c r="A19" s="10">
         <v>15</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C19" s="12">
         <v>46328</v>
@@ -1163,7 +1121,7 @@
         <v>46338</v>
       </c>
       <c r="E19" s="10">
-        <f t="shared" si="0"/>
+        <f>D19-C19+1</f>
         <v>11</v>
       </c>
       <c r="F19" s="10"/>
@@ -1176,12 +1134,12 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="10">
         <v>16</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C20" s="12">
         <v>46329</v>
@@ -1190,7 +1148,7 @@
         <v>46329</v>
       </c>
       <c r="E20" s="10">
-        <f t="shared" si="0"/>
+        <f>D20-C20+1</f>
         <v>1</v>
       </c>
       <c r="F20" s="10"/>
@@ -1203,12 +1161,12 @@
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="19.5" customHeight="1">
       <c r="A21" s="10">
         <v>17</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C21" s="12">
         <v>46331</v>
@@ -1217,7 +1175,7 @@
         <v>46335</v>
       </c>
       <c r="E21" s="10">
-        <f t="shared" si="0"/>
+        <f>D21-C21+1</f>
         <v>5</v>
       </c>
       <c r="F21" s="10"/>
@@ -1230,12 +1188,12 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="10">
         <v>18</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>39</v>
+      <c r="B22" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="C22" s="12">
         <v>46332</v>
@@ -1244,7 +1202,7 @@
         <v>46335</v>
       </c>
       <c r="E22" s="10">
-        <f t="shared" si="0"/>
+        <f>D22-C22+1</f>
         <v>4</v>
       </c>
       <c r="F22" s="10"/>
@@ -1257,12 +1215,12 @@
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="19.5" customHeight="1">
       <c r="A23" s="10">
         <v>19</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>40</v>
+      <c r="B23" s="13" t="s">
+        <v>35</v>
       </c>
       <c r="C23" s="12">
         <v>46335</v>
@@ -1271,7 +1229,7 @@
         <v>46339</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="0"/>
+        <f>D23-C23+1</f>
         <v>5</v>
       </c>
       <c r="F23" s="10"/>
@@ -1284,12 +1242,12 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="19.5" customHeight="1">
       <c r="A24" s="10">
         <v>20</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C24" s="12">
         <v>46335</v>
@@ -1298,7 +1256,7 @@
         <v>46348</v>
       </c>
       <c r="E24" s="10">
-        <f t="shared" si="0"/>
+        <f>D24-C24+1</f>
         <v>14</v>
       </c>
       <c r="F24" s="10"/>
@@ -1311,12 +1269,12 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
     </row>
-    <row r="25" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="10">
         <v>21</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>41</v>
+      <c r="B25" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="C25" s="12">
         <v>46338</v>
@@ -1325,7 +1283,7 @@
         <v>46347</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="0"/>
+        <f>D25-C25+1</f>
         <v>10</v>
       </c>
       <c r="F25" s="10"/>
@@ -1338,12 +1296,12 @@
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="10">
         <v>22</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>42</v>
+      <c r="B26" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="C26" s="12">
         <v>46339</v>
@@ -1352,7 +1310,7 @@
         <v>46348</v>
       </c>
       <c r="E26" s="10">
-        <f t="shared" si="0"/>
+        <f>D26-C26+1</f>
         <v>10</v>
       </c>
       <c r="F26" s="10"/>
@@ -1365,12 +1323,12 @@
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="10">
         <v>23</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>43</v>
+      <c r="B27" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="C27" s="12">
         <v>46340</v>
@@ -1379,7 +1337,7 @@
         <v>46346</v>
       </c>
       <c r="E27" s="10">
-        <f t="shared" si="0"/>
+        <f>D27-C27+1</f>
         <v>7</v>
       </c>
       <c r="F27" s="10"/>
@@ -1392,12 +1350,12 @@
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="10">
         <v>24</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>44</v>
+      <c r="B28" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="C28" s="12">
         <v>46349</v>
@@ -1406,7 +1364,7 @@
         <v>46349</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="0"/>
+        <f>D28-C28+1</f>
         <v>1</v>
       </c>
       <c r="F28" s="10"/>
@@ -1419,12 +1377,12 @@
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
     </row>
-    <row r="29" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="10">
         <v>25</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>45</v>
+      <c r="B29" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="C29" s="12">
         <v>46349</v>
@@ -1433,7 +1391,7 @@
         <v>46352</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="0"/>
+        <f>D29-C29+1</f>
         <v>4</v>
       </c>
       <c r="F29" s="10"/>
@@ -1446,12 +1404,12 @@
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
-    <row r="30" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="10">
         <v>26</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C30" s="12">
         <v>46352</v>
@@ -1460,7 +1418,7 @@
         <v>46352</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="0"/>
+        <f>D30-C30+1</f>
         <v>1</v>
       </c>
       <c r="F30" s="10"/>
@@ -1473,49 +1431,51 @@
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="B32" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="15"/>
       <c r="B33" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="16"/>
       <c r="B34" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="17"/>
       <c r="B35" s="3" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A7:E30">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>LEFT($B7,1)="◆"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:N6">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>AND(TODAY()&gt;=F$6,TODAY()&lt;=F$6+6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:N30">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>AND(LEFT($B7,1)="◆",AND(F$6&lt;=$D7,F$6+6&gt;=$C7))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:N30">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(F$6&lt;=$D7,F$6+6&gt;=$C7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5118110179901123" footer="0.5118110179901123"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>